--- a/config/A2700/Demo_Test_A2700M.xlsx
+++ b/config/A2700/Demo_Test_A2700M.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PNT\61.AI\VisionOCR\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PNT\61.AI\VisionOCR\config\A2700\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99983C7C-0437-43FE-8460-9314D495F8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E944DC7F-0E32-41DA-A094-D2B5E994D58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4680" yWindow="-22020" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="231">
   <si>
     <t>name</t>
   </si>
@@ -297,9 +297,6 @@
     <t>5; 5; 5; 5</t>
   </si>
   <si>
-    <t>L-N, L-L, U0, U2</t>
-  </si>
-  <si>
     <t>4057; 4059; 4061; 4063</t>
   </si>
   <si>
@@ -339,24 +336,9 @@
     <t>335, 65</t>
   </si>
   <si>
-    <t>Phase Current,Max,A,B,C,AVG</t>
-  </si>
-  <si>
-    <t>23.0; 23.0; 23.0; 23.0</t>
-  </si>
-  <si>
-    <t>25.0; 25.0; 25.0; 25.0</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
-    <t>45.0; 45.0; 45.0; 45.0</t>
-  </si>
-  <si>
-    <t>55.0; 55.0; 55.0; 55.0</t>
-  </si>
-  <si>
     <t>4073; 4075; 4077; 4079</t>
   </si>
   <si>
@@ -366,27 +348,18 @@
     <t>CURRENT-Phase-Max</t>
   </si>
   <si>
-    <t>Phase Current Max.,A,B,C,AVG</t>
-  </si>
-  <si>
     <t>60040; 60042; 60044; 60046</t>
   </si>
   <si>
     <t>CURRENT-Fund</t>
   </si>
   <si>
-    <t>Fundamental Current,A,B,C,AVG</t>
-  </si>
-  <si>
     <t>4081; 4083; 4085; 4087</t>
   </si>
   <si>
     <t>CURRENT-Demand</t>
   </si>
   <si>
-    <t>Demand Current,Peak,A,B,C,AVG</t>
-  </si>
-  <si>
     <t>4181; 4183; 4185; 4187</t>
   </si>
   <si>
@@ -396,9 +369,6 @@
     <t>Peak</t>
   </si>
   <si>
-    <t>Demand Current Peak,A,B,C,AVG</t>
-  </si>
-  <si>
     <t>60116; 60118; 60120; 60122</t>
   </si>
   <si>
@@ -408,45 +378,30 @@
     <t>CURRENT-THD</t>
   </si>
   <si>
-    <t>Total Harmonic Distortion,Max,A,B,C</t>
-  </si>
-  <si>
     <t>4113; 4115; 4117</t>
   </si>
   <si>
     <t>CURRENT-THD-Max</t>
   </si>
   <si>
-    <t>Total Harmonic Distortion Max.,A,B,C</t>
-  </si>
-  <si>
     <t>60060; 60062; 60064</t>
   </si>
   <si>
     <t>CURRENT-TDD</t>
   </si>
   <si>
-    <t>Total Demand Distortion,Max,A,B,C</t>
-  </si>
-  <si>
     <t>4119; 4121; 4123</t>
   </si>
   <si>
     <t>CURRENT-TDD-Max</t>
   </si>
   <si>
-    <t>Total Demand Distortion Max.,A,B,C</t>
-  </si>
-  <si>
     <t>60066; 60068; 60070</t>
   </si>
   <si>
     <t>CURRENT-Unbal</t>
   </si>
   <si>
-    <t>Unbalance Current,Max,NEMA,Phase,Zero-Sequence,U0,Negative-Sequence,U2</t>
-  </si>
-  <si>
     <t>0; 0; 0</t>
   </si>
   <si>
@@ -456,9 +411,6 @@
     <t>CURRENT-Unbal-Max</t>
   </si>
   <si>
-    <t>Unbalance Current Max.,NEMA,Phase,Zero-Sequence,U0,Negative-Sequence,U2</t>
-  </si>
-  <si>
     <t>60054; 60056; 60058</t>
   </si>
   <si>
@@ -468,15 +420,9 @@
     <t>65, 345</t>
   </si>
   <si>
-    <t>Crest Factor,Max,A,B,C</t>
-  </si>
-  <si>
     <t>1.300; 1.300; 1.300</t>
   </si>
   <si>
-    <t>1.600; 1.600; 1.600</t>
-  </si>
-  <si>
     <t>4125; 4127; 4129</t>
   </si>
   <si>
@@ -486,9 +432,6 @@
     <t>CURRENT-CF-Max</t>
   </si>
   <si>
-    <t>Crest Factor Max.,A,B,C</t>
-  </si>
-  <si>
     <t>60072; 60074; 60076</t>
   </si>
   <si>
@@ -498,15 +441,9 @@
     <t>65, 385</t>
   </si>
   <si>
-    <t>K-Factor,Max,A,B,C</t>
-  </si>
-  <si>
     <t>0.900; 0.900; 0.900</t>
   </si>
   <si>
-    <t>1.500; 1.500; 1.500</t>
-  </si>
-  <si>
     <t>4131; 4133; 4135</t>
   </si>
   <si>
@@ -516,9 +453,6 @@
     <t>CURRENT-KF-Max</t>
   </si>
   <si>
-    <t>K-Factor Max.,A,B,C</t>
-  </si>
-  <si>
     <t>60078; 60080; 60082</t>
   </si>
   <si>
@@ -528,27 +462,9 @@
     <t>470, 65</t>
   </si>
   <si>
-    <t>Active Power,Max,A,B,C,TOTAL</t>
-  </si>
-  <si>
-    <t>5000; 5000; 5000; 15000</t>
-  </si>
-  <si>
-    <t>5600; 5600; 5600; 16800</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
     <t>4137; 4139; 4141; 4143</t>
   </si>
   <si>
-    <t>5.0; 5.0; 5.0; 15.0</t>
-  </si>
-  <si>
-    <t>5.6; 5.6; 5.6; 16.8</t>
-  </si>
-  <si>
     <t>kW</t>
   </si>
   <si>
@@ -558,18 +474,12 @@
     <t>POWER-P-Max</t>
   </si>
   <si>
-    <t>Active Power Max.,A,B,C,TOTAL</t>
-  </si>
-  <si>
     <t>60084; 60086; 60088; 60090</t>
   </si>
   <si>
     <t>POWER-Q</t>
   </si>
   <si>
-    <t>Reactive Power,Max,A,B,C,TOTAL</t>
-  </si>
-  <si>
     <t>-100; -100; -100; -100</t>
   </si>
   <si>
@@ -597,21 +507,12 @@
     <t>POWER-Q-Max</t>
   </si>
   <si>
-    <t>Reactive Power Max.,A,B,C,TOTAL</t>
-  </si>
-  <si>
     <t>60092; 60094; 60096; 60098</t>
   </si>
   <si>
     <t>POWER-S</t>
   </si>
   <si>
-    <t>Apparent Power,Max,A,B,C,TOTAL</t>
-  </si>
-  <si>
-    <t>VA</t>
-  </si>
-  <si>
     <t>4153; 4155; 4157; 4159</t>
   </si>
   <si>
@@ -621,18 +522,12 @@
     <t>POWER-S-Max</t>
   </si>
   <si>
-    <t>Apparent Power Max.,A,B,C,TOTAL</t>
-  </si>
-  <si>
     <t>60100; 60102; 60104; 60106</t>
   </si>
   <si>
     <t>POWER-PF</t>
   </si>
   <si>
-    <t>Power Factor,A,B,C,TOTAL</t>
-  </si>
-  <si>
     <t>0.950; 0.950; 0.950; 0.950</t>
   </si>
   <si>
@@ -645,30 +540,15 @@
     <t>PF 화면은 Max 버튼 없음</t>
   </si>
   <si>
-    <t>POWER-DemandP</t>
-  </si>
-  <si>
-    <t>Demand Active Power,Peak,A,B,C,TOTAL</t>
-  </si>
-  <si>
     <t>4173; 4175; 4177; 4179</t>
   </si>
   <si>
-    <t>POWER-DemandP-Peak</t>
-  </si>
-  <si>
-    <t>Demand Active Power Peak,A,B,C,TOTAL</t>
-  </si>
-  <si>
     <t>60108; 60110; 60112; 60114</t>
   </si>
   <si>
     <t>POWER-EnergyP</t>
   </si>
   <si>
-    <t>Active Energy,REC,DEL,NET,SUM</t>
-  </si>
-  <si>
     <t>kWh</t>
   </si>
   <si>
@@ -678,9 +558,6 @@
     <t>POWER-EnergyQ</t>
   </si>
   <si>
-    <t>Reactive Energy,REC,DEL,NET,SUM</t>
-  </si>
-  <si>
     <t>kVARh</t>
   </si>
   <si>
@@ -725,6 +602,170 @@
   </si>
   <si>
     <t>0; 0; 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phase Current, Max, A, B, C, AVG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.000; 4.000; 4.000; 4.000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.000; 6.000; 6.000; 6.000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99.0; 99.0; 99.0; 99.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101.0; 101.0; 101.0; 101.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Peak Demand Current, Peak, A, B, C, AVG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demand Current, Peak, A, B, C, AVG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fundamental Current, A, B, C, AVG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total Harmonic Distortion Max, Max, A, B, C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total Harmonic Distortion, Max, A, B, C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total Demand Distortion, Max, A, B, C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total Demand Distortion Max, Max, A, B, C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unbalance Current, Max, NEMA, Zero-, Sequence, Negative-, Sequence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unbalance Current Max, Max, NEMA, Zero-, Sequence, Negative-, Sequence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crest Factor, Max, A, B, C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.000; 2.000; 2.000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.000; 1.000; 1.000; 3.000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.200; 1.200; 1.200; 3.500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-Factor, Max, A, B, C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-Factor Max, Max, A, B, C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Active Power, Max, A, B, C, TOTAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Active Power Max, Max, A, B, C, TOTAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reactive Power, Max ,A, B, C, TOTAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reactive Power Max, Max, A, B, C, TOTAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Apparent Power, Max, A, B, C, TOTAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Apparent Power Max, Max, A, B, C, TOTAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kVA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demand Active Power, Peak, A, B, C, TOTAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Peak Demand Active Power, Peak, A, B, C, TOTAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Active Energy, REC, DEL, NET, SUM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reactive Energy, REC, DEL, NET, SUM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phase Current Max, Max, A, B, C, AVG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crest Factor Max, Max, A, B, C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POWER-Demand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POWER-Demand-Peak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power Factor, A, B, C, TOTAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LEAD|LAG; LEAD|LAG; LEAD|LAG; LEAD|LAG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demand Reset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phase, U0|UO, U2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L-N, L-L, U0|UO, U2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1161,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y40"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -1333,77 +1374,41 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="B3" t="s">
-        <v>229</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" t="b">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" t="s">
-        <v>52</v>
-      </c>
-      <c r="L4" t="s">
-        <v>53</v>
-      </c>
-      <c r="S4" t="s">
-        <v>54</v>
-      </c>
-      <c r="T4" t="s">
-        <v>55</v>
-      </c>
-      <c r="U4" t="s">
-        <v>51</v>
-      </c>
-      <c r="V4" t="s">
-        <v>52</v>
-      </c>
-      <c r="W4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>56</v>
+        <v>228</v>
+      </c>
+      <c r="B4" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
       </c>
-      <c r="G5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H5" t="s">
-        <v>59</v>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
       </c>
       <c r="I5" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J5" t="s">
         <v>51</v>
@@ -1414,11 +1419,8 @@
       <c r="L5" t="s">
         <v>53</v>
       </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
       <c r="S5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="T5" t="s">
         <v>55</v>
@@ -1433,71 +1435,74 @@
         <v>53</v>
       </c>
       <c r="Y5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B6" t="b">
         <v>1</v>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
+      <c r="G6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" t="s">
+        <v>59</v>
       </c>
       <c r="I6" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J6" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="K6" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="L6" t="s">
         <v>53</v>
       </c>
       <c r="S6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="T6" t="s">
         <v>55</v>
       </c>
       <c r="U6" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="V6" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="W6" t="s">
         <v>53</v>
       </c>
+      <c r="Y6" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
       </c>
-      <c r="G7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H7" t="s">
-        <v>59</v>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>65</v>
       </c>
       <c r="I7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="J7" t="s">
         <v>67</v>
@@ -1508,11 +1513,8 @@
       <c r="L7" t="s">
         <v>53</v>
       </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
       <c r="S7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="T7" t="s">
         <v>55</v>
@@ -1529,57 +1531,48 @@
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B8" t="b">
         <v>1</v>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8" t="s">
-        <v>74</v>
+      <c r="G8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" t="s">
+        <v>59</v>
       </c>
       <c r="I8" t="s">
-        <v>223</v>
+        <v>71</v>
       </c>
       <c r="J8" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="K8" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="L8" t="s">
         <v>53</v>
       </c>
       <c r="S8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="T8" t="s">
         <v>55</v>
       </c>
       <c r="U8" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="V8" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="W8" t="s">
         <v>53</v>
       </c>
-      <c r="Y8" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B9" t="b">
         <v>1</v>
@@ -1591,78 +1584,84 @@
         <v>64</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I9" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="J9" t="s">
-        <v>230</v>
+        <v>51</v>
       </c>
       <c r="K9" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="L9" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="S9" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="T9" t="s">
         <v>55</v>
       </c>
       <c r="U9" t="s">
-        <v>230</v>
+        <v>51</v>
       </c>
       <c r="V9" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="W9" t="s">
-        <v>81</v>
+        <v>53</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B10" t="b">
         <v>1</v>
       </c>
-      <c r="G10" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" t="s">
-        <v>59</v>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10" t="s">
+        <v>78</v>
       </c>
       <c r="I10" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="J10" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="K10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L10" t="s">
         <v>81</v>
       </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
       <c r="S10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="T10" t="s">
         <v>55</v>
       </c>
       <c r="U10" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="V10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="W10" t="s">
         <v>81</v>
@@ -1670,49 +1669,40 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>
       </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>87</v>
+      <c r="G11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" t="s">
+        <v>59</v>
       </c>
       <c r="I11" t="s">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="J11" t="s">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="K11" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="L11" t="s">
         <v>81</v>
       </c>
-      <c r="O11" t="s">
-        <v>90</v>
-      </c>
       <c r="S11" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="T11" t="s">
         <v>55</v>
       </c>
       <c r="U11" t="s">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="V11" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="W11" t="s">
         <v>81</v>
@@ -1720,19 +1710,25 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B12" t="b">
         <v>1</v>
       </c>
-      <c r="G12" t="s">
-        <v>58</v>
-      </c>
-      <c r="H12" t="s">
-        <v>59</v>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>87</v>
       </c>
       <c r="I12" t="s">
-        <v>227</v>
+        <v>185</v>
       </c>
       <c r="J12" t="s">
         <v>88</v>
@@ -1744,13 +1740,10 @@
         <v>81</v>
       </c>
       <c r="O12" t="s">
+        <v>230</v>
+      </c>
+      <c r="S12" t="s">
         <v>90</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>1</v>
-      </c>
-      <c r="S12" t="s">
-        <v>93</v>
       </c>
       <c r="T12" t="s">
         <v>55</v>
@@ -1767,228 +1760,210 @@
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B13" t="b">
         <v>1</v>
       </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>95</v>
+      <c r="G13" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" t="s">
+        <v>59</v>
       </c>
       <c r="I13" t="s">
-        <v>96</v>
+        <v>186</v>
       </c>
       <c r="J13" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="L13" t="s">
-        <v>99</v>
+        <v>81</v>
+      </c>
+      <c r="O13" t="s">
+        <v>230</v>
       </c>
       <c r="S13" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="T13" t="s">
         <v>55</v>
       </c>
       <c r="U13" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="V13" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="W13" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B14" t="b">
         <v>1</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="I14" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="J14" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="K14" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="L14" t="s">
-        <v>107</v>
-      </c>
-      <c r="M14" t="s">
-        <v>108</v>
-      </c>
-      <c r="N14" t="s">
-        <v>109</v>
-      </c>
-      <c r="P14" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="S14" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="T14" t="s">
         <v>55</v>
       </c>
       <c r="U14" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="V14" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="W14" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="Y14" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B15" t="b">
         <v>1</v>
       </c>
-      <c r="G15" t="s">
-        <v>58</v>
-      </c>
-      <c r="H15" t="s">
-        <v>59</v>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>49</v>
       </c>
       <c r="I15" t="s">
-        <v>113</v>
+        <v>190</v>
       </c>
       <c r="J15" t="s">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="K15" t="s">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="L15" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="M15" t="s">
-        <v>108</v>
+        <v>193</v>
       </c>
       <c r="N15" t="s">
-        <v>109</v>
+        <v>194</v>
       </c>
       <c r="P15" t="s">
         <v>81</v>
       </c>
-      <c r="Q15" t="b">
-        <v>1</v>
-      </c>
       <c r="S15" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="T15" t="s">
         <v>55</v>
       </c>
       <c r="U15" t="s">
+        <v>191</v>
+      </c>
+      <c r="V15" t="s">
+        <v>192</v>
+      </c>
+      <c r="W15" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y15" t="s">
         <v>105</v>
-      </c>
-      <c r="V15" t="s">
-        <v>106</v>
-      </c>
-      <c r="W15" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B16" t="b">
         <v>1</v>
       </c>
-      <c r="C16">
-        <v>3</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="G16" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" t="s">
+        <v>222</v>
+      </c>
+      <c r="J16" t="s">
+        <v>191</v>
+      </c>
+      <c r="K16" t="s">
+        <v>192</v>
+      </c>
+      <c r="L16" t="s">
         <v>103</v>
       </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-      <c r="I16" t="s">
-        <v>116</v>
-      </c>
-      <c r="J16" t="s">
-        <v>105</v>
-      </c>
-      <c r="K16" t="s">
-        <v>106</v>
-      </c>
-      <c r="L16" t="s">
-        <v>107</v>
-      </c>
       <c r="M16" t="s">
-        <v>108</v>
+        <v>193</v>
       </c>
       <c r="N16" t="s">
-        <v>109</v>
+        <v>194</v>
       </c>
       <c r="P16" t="s">
         <v>81</v>
       </c>
       <c r="S16" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="T16" t="s">
         <v>55</v>
       </c>
       <c r="U16" t="s">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="V16" t="s">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="W16" t="s">
-        <v>107</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B17" t="b">
         <v>1</v>
@@ -1997,140 +1972,128 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" t="s">
+        <v>197</v>
+      </c>
+      <c r="J17" t="s">
+        <v>191</v>
+      </c>
+      <c r="K17" t="s">
+        <v>192</v>
+      </c>
+      <c r="L17" t="s">
         <v>103</v>
       </c>
-      <c r="E17">
-        <v>3</v>
-      </c>
-      <c r="F17" t="s">
-        <v>74</v>
-      </c>
-      <c r="I17" t="s">
-        <v>119</v>
-      </c>
-      <c r="J17" t="s">
-        <v>105</v>
-      </c>
-      <c r="K17" t="s">
-        <v>106</v>
-      </c>
-      <c r="L17" t="s">
-        <v>107</v>
-      </c>
       <c r="M17" t="s">
-        <v>108</v>
+        <v>193</v>
       </c>
       <c r="N17" t="s">
-        <v>109</v>
+        <v>194</v>
       </c>
       <c r="P17" t="s">
         <v>81</v>
       </c>
       <c r="S17" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="T17" t="s">
         <v>55</v>
       </c>
       <c r="U17" t="s">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="V17" t="s">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="W17" t="s">
-        <v>107</v>
+        <v>103</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B18" t="b">
         <v>1</v>
       </c>
-      <c r="G18" t="s">
-        <v>122</v>
-      </c>
-      <c r="H18" t="s">
-        <v>59</v>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18" t="s">
+        <v>78</v>
       </c>
       <c r="I18" t="s">
-        <v>123</v>
+        <v>199</v>
       </c>
       <c r="J18" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="K18" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="L18" t="s">
-        <v>107</v>
-      </c>
-      <c r="M18" t="s">
-        <v>108</v>
-      </c>
-      <c r="N18" t="s">
-        <v>109</v>
-      </c>
-      <c r="P18" t="s">
         <v>81</v>
       </c>
-      <c r="Q18" t="b">
-        <v>1</v>
-      </c>
       <c r="S18" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="T18" t="s">
         <v>55</v>
       </c>
       <c r="U18" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="V18" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="W18" t="s">
-        <v>107</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B19" t="b">
         <v>1</v>
       </c>
-      <c r="C19">
-        <v>3</v>
-      </c>
-      <c r="D19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19">
-        <v>4</v>
-      </c>
-      <c r="F19" t="s">
-        <v>78</v>
+      <c r="G19" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" t="s">
+        <v>59</v>
       </c>
       <c r="I19" t="s">
-        <v>127</v>
+        <v>198</v>
       </c>
       <c r="J19" t="s">
         <v>79</v>
       </c>
       <c r="K19" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L19" t="s">
         <v>81</v>
       </c>
       <c r="S19" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="T19" t="s">
         <v>55</v>
@@ -2139,7 +2102,7 @@
         <v>79</v>
       </c>
       <c r="V19" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="W19" t="s">
         <v>81</v>
@@ -2147,34 +2110,37 @@
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B20" t="b">
         <v>1</v>
       </c>
-      <c r="G20" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" t="s">
-        <v>59</v>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>87</v>
       </c>
       <c r="I20" t="s">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="J20" t="s">
         <v>79</v>
       </c>
       <c r="K20" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L20" t="s">
         <v>81</v>
       </c>
-      <c r="Q20" t="b">
-        <v>1</v>
-      </c>
       <c r="S20" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="T20" t="s">
         <v>55</v>
@@ -2183,7 +2149,7 @@
         <v>79</v>
       </c>
       <c r="V20" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="W20" t="s">
         <v>81</v>
@@ -2191,37 +2157,31 @@
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B21" t="b">
         <v>1</v>
       </c>
-      <c r="C21">
-        <v>3</v>
-      </c>
-      <c r="D21" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>87</v>
+      <c r="G21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H21" t="s">
+        <v>59</v>
       </c>
       <c r="I21" t="s">
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="J21" t="s">
         <v>79</v>
       </c>
       <c r="K21" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L21" t="s">
         <v>81</v>
       </c>
       <c r="S21" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="T21" t="s">
         <v>55</v>
@@ -2230,7 +2190,7 @@
         <v>79</v>
       </c>
       <c r="V21" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="W21" t="s">
         <v>81</v>
@@ -2238,43 +2198,49 @@
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B22" t="b">
         <v>1</v>
       </c>
-      <c r="G22" t="s">
-        <v>58</v>
-      </c>
-      <c r="H22" t="s">
-        <v>59</v>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22">
+        <v>6</v>
+      </c>
+      <c r="F22" t="s">
+        <v>94</v>
       </c>
       <c r="I22" t="s">
-        <v>136</v>
+        <v>202</v>
       </c>
       <c r="J22" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="K22" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L22" t="s">
         <v>81</v>
       </c>
-      <c r="Q22" t="b">
-        <v>1</v>
+      <c r="O22" t="s">
+        <v>229</v>
       </c>
       <c r="S22" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="T22" t="s">
         <v>55</v>
       </c>
       <c r="U22" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="V22" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="W22" t="s">
         <v>81</v>
@@ -2282,28 +2248,22 @@
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B23" t="b">
         <v>1</v>
       </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23" t="s">
-        <v>103</v>
-      </c>
-      <c r="E23">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>95</v>
+      <c r="G23" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" t="s">
+        <v>59</v>
       </c>
       <c r="I23" t="s">
-        <v>139</v>
+        <v>203</v>
       </c>
       <c r="J23" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="K23" t="s">
         <v>80</v>
@@ -2311,14 +2271,17 @@
       <c r="L23" t="s">
         <v>81</v>
       </c>
+      <c r="O23" t="s">
+        <v>229</v>
+      </c>
       <c r="S23" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="T23" t="s">
         <v>55</v>
       </c>
       <c r="U23" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="V23" t="s">
         <v>80</v>
@@ -2329,494 +2292,482 @@
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="B24" t="b">
         <v>1</v>
       </c>
-      <c r="G24" t="s">
-        <v>58</v>
-      </c>
-      <c r="H24" t="s">
-        <v>59</v>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>130</v>
       </c>
       <c r="I24" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="J24" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="K24" t="s">
-        <v>80</v>
-      </c>
-      <c r="L24" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>1</v>
+        <v>205</v>
       </c>
       <c r="S24" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="T24" t="s">
         <v>55</v>
       </c>
       <c r="U24" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="V24" t="s">
-        <v>80</v>
-      </c>
-      <c r="W24" t="s">
-        <v>81</v>
+        <v>205</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="B25" t="b">
         <v>1</v>
       </c>
-      <c r="C25">
-        <v>3</v>
-      </c>
-      <c r="D25" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>146</v>
+      <c r="G25" t="s">
+        <v>58</v>
+      </c>
+      <c r="H25" t="s">
+        <v>59</v>
       </c>
       <c r="I25" t="s">
-        <v>147</v>
+        <v>223</v>
       </c>
       <c r="J25" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="K25" t="s">
-        <v>149</v>
+        <v>205</v>
       </c>
       <c r="S25" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="T25" t="s">
         <v>55</v>
       </c>
       <c r="U25" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="V25" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>151</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="B26" t="b">
         <v>1</v>
       </c>
-      <c r="G26" t="s">
-        <v>58</v>
-      </c>
-      <c r="H26" t="s">
-        <v>59</v>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>137</v>
       </c>
       <c r="I26" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
       <c r="J26" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="K26" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>1</v>
+        <v>205</v>
       </c>
       <c r="S26" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="T26" t="s">
         <v>55</v>
       </c>
       <c r="U26" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="V26" t="s">
-        <v>149</v>
+        <v>205</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="B27" t="b">
         <v>1</v>
       </c>
-      <c r="C27">
-        <v>3</v>
-      </c>
-      <c r="D27" t="s">
-        <v>103</v>
-      </c>
-      <c r="E27">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>156</v>
+      <c r="G27" t="s">
+        <v>58</v>
+      </c>
+      <c r="H27" t="s">
+        <v>59</v>
       </c>
       <c r="I27" t="s">
-        <v>157</v>
+        <v>210</v>
       </c>
       <c r="J27" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="K27" t="s">
-        <v>159</v>
+        <v>205</v>
       </c>
       <c r="S27" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="T27" t="s">
         <v>55</v>
       </c>
       <c r="U27" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="V27" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>161</v>
+        <v>205</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="B28" t="b">
         <v>1</v>
       </c>
-      <c r="G28" t="s">
-        <v>58</v>
-      </c>
-      <c r="H28" t="s">
-        <v>59</v>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>144</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s">
+        <v>49</v>
       </c>
       <c r="I28" t="s">
-        <v>163</v>
+        <v>211</v>
       </c>
       <c r="J28" t="s">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="K28" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="L28" t="s">
+        <v>206</v>
       </c>
       <c r="S28" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="T28" t="s">
         <v>55</v>
       </c>
       <c r="U28" t="s">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="V28" t="s">
-        <v>159</v>
+        <v>208</v>
+      </c>
+      <c r="W28" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="B29" t="b">
         <v>1</v>
       </c>
-      <c r="C29">
-        <v>4</v>
-      </c>
-      <c r="D29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29" t="s">
-        <v>49</v>
+      <c r="G29" t="s">
+        <v>58</v>
+      </c>
+      <c r="H29" t="s">
+        <v>59</v>
       </c>
       <c r="I29" t="s">
-        <v>167</v>
+        <v>212</v>
       </c>
       <c r="J29" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="K29" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="L29" t="s">
-        <v>170</v>
+        <v>206</v>
       </c>
       <c r="S29" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="T29" t="s">
         <v>55</v>
       </c>
       <c r="U29" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="V29" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="W29" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="B30" t="b">
         <v>1</v>
       </c>
-      <c r="G30" t="s">
-        <v>58</v>
-      </c>
-      <c r="H30" t="s">
-        <v>59</v>
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>144</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30" t="s">
+        <v>65</v>
       </c>
       <c r="I30" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="J30" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="K30" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="L30" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="S30" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="T30" t="s">
         <v>55</v>
       </c>
       <c r="U30" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="V30" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="W30" t="s">
-        <v>174</v>
+        <v>157</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="B31" t="b">
         <v>1</v>
       </c>
-      <c r="C31">
-        <v>4</v>
-      </c>
-      <c r="D31" t="s">
-        <v>166</v>
-      </c>
-      <c r="E31">
-        <v>2</v>
-      </c>
-      <c r="F31" t="s">
-        <v>65</v>
+      <c r="G31" t="s">
+        <v>58</v>
+      </c>
+      <c r="H31" t="s">
+        <v>59</v>
       </c>
       <c r="I31" t="s">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="J31" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="K31" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="L31" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
       <c r="S31" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="T31" t="s">
         <v>55</v>
       </c>
       <c r="U31" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="V31" t="s">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="W31" t="s">
-        <v>187</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="B32" t="b">
         <v>1</v>
       </c>
-      <c r="G32" t="s">
-        <v>58</v>
-      </c>
-      <c r="H32" t="s">
-        <v>59</v>
+      <c r="C32">
+        <v>4</v>
+      </c>
+      <c r="D32" t="s">
+        <v>144</v>
+      </c>
+      <c r="E32">
+        <v>3</v>
+      </c>
+      <c r="F32" t="s">
+        <v>74</v>
       </c>
       <c r="I32" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="J32" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="K32" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="L32" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q32" t="b">
-        <v>1</v>
+        <v>217</v>
       </c>
       <c r="S32" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="T32" t="s">
         <v>55</v>
       </c>
       <c r="U32" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="V32" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="W32" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="B33" t="b">
         <v>1</v>
       </c>
-      <c r="C33">
-        <v>4</v>
-      </c>
-      <c r="D33" t="s">
-        <v>166</v>
-      </c>
-      <c r="E33">
-        <v>3</v>
-      </c>
-      <c r="F33" t="s">
-        <v>74</v>
+      <c r="G33" t="s">
+        <v>58</v>
+      </c>
+      <c r="H33" t="s">
+        <v>59</v>
       </c>
       <c r="I33" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="J33" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="K33" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="L33" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="S33" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="T33" t="s">
         <v>55</v>
       </c>
       <c r="U33" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="V33" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="W33" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B34" t="b">
         <v>1</v>
       </c>
-      <c r="G34" t="s">
-        <v>58</v>
-      </c>
-      <c r="H34" t="s">
-        <v>59</v>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>144</v>
+      </c>
+      <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34" t="s">
+        <v>78</v>
       </c>
       <c r="I34" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="J34" t="s">
+        <v>167</v>
+      </c>
+      <c r="K34" t="s">
         <v>168</v>
       </c>
-      <c r="K34" t="s">
+      <c r="O34" t="s">
+        <v>227</v>
+      </c>
+      <c r="S34" t="s">
         <v>169</v>
       </c>
-      <c r="L34" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q34" t="b">
-        <v>1</v>
-      </c>
-      <c r="S34" t="s">
-        <v>199</v>
-      </c>
       <c r="T34" t="s">
         <v>55</v>
       </c>
       <c r="U34" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="V34" t="s">
-        <v>173</v>
-      </c>
-      <c r="W34" t="s">
-        <v>196</v>
+        <v>168</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="B35" t="b">
         <v>1</v>
@@ -2825,42 +2776,27 @@
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s">
-        <v>201</v>
-      </c>
-      <c r="J35" t="s">
-        <v>202</v>
-      </c>
-      <c r="K35" t="s">
-        <v>203</v>
-      </c>
-      <c r="S35" t="s">
-        <v>204</v>
-      </c>
-      <c r="T35" t="s">
-        <v>55</v>
-      </c>
-      <c r="U35" t="s">
-        <v>202</v>
-      </c>
-      <c r="V35" t="s">
-        <v>203</v>
+        <v>220</v>
+      </c>
+      <c r="L35" t="s">
+        <v>174</v>
       </c>
       <c r="Y35" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="B36" t="b">
         <v>1</v>
@@ -2869,147 +2805,162 @@
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>87</v>
+        <v>130</v>
       </c>
       <c r="I36" t="s">
-        <v>207</v>
-      </c>
-      <c r="J36" t="s">
-        <v>168</v>
-      </c>
-      <c r="K36" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="L36" t="s">
-        <v>170</v>
-      </c>
-      <c r="S36" t="s">
-        <v>208</v>
-      </c>
-      <c r="T36" t="s">
-        <v>55</v>
-      </c>
-      <c r="U36" t="s">
-        <v>172</v>
-      </c>
-      <c r="V36" t="s">
-        <v>173</v>
-      </c>
-      <c r="W36" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="B37" t="b">
         <v>1</v>
       </c>
-      <c r="G37" t="s">
-        <v>122</v>
-      </c>
-      <c r="H37" t="s">
-        <v>59</v>
+      <c r="C37">
+        <v>4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>144</v>
+      </c>
+      <c r="E37">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>137</v>
       </c>
       <c r="I37" t="s">
-        <v>210</v>
-      </c>
-      <c r="J37" t="s">
-        <v>168</v>
-      </c>
-      <c r="K37" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="L37" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q37" t="b">
-        <v>1</v>
-      </c>
-      <c r="S37" t="s">
-        <v>211</v>
-      </c>
-      <c r="T37" t="s">
-        <v>55</v>
-      </c>
-      <c r="U37" t="s">
-        <v>172</v>
-      </c>
-      <c r="V37" t="s">
-        <v>173</v>
-      </c>
-      <c r="W37" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="Y37" t="s">
-        <v>125</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>212</v>
+        <v>110</v>
       </c>
       <c r="B38" t="b">
         <v>1</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
       <c r="E38">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="I38" t="s">
-        <v>213</v>
+        <v>196</v>
+      </c>
+      <c r="J38" t="s">
+        <v>191</v>
+      </c>
+      <c r="K38" t="s">
+        <v>192</v>
       </c>
       <c r="L38" t="s">
-        <v>214</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>215</v>
+        <v>103</v>
+      </c>
+      <c r="M38" t="s">
+        <v>193</v>
+      </c>
+      <c r="N38" t="s">
+        <v>194</v>
+      </c>
+      <c r="P38" t="s">
+        <v>81</v>
+      </c>
+      <c r="S38" t="s">
+        <v>111</v>
+      </c>
+      <c r="T38" t="s">
+        <v>55</v>
+      </c>
+      <c r="U38" t="s">
+        <v>191</v>
+      </c>
+      <c r="V38" t="s">
+        <v>192</v>
+      </c>
+      <c r="W38" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="B39" t="b">
         <v>1</v>
       </c>
-      <c r="C39">
-        <v>4</v>
-      </c>
-      <c r="D39" t="s">
-        <v>166</v>
-      </c>
-      <c r="E39">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>146</v>
+      <c r="G39" t="s">
+        <v>113</v>
+      </c>
+      <c r="H39" t="s">
+        <v>59</v>
       </c>
       <c r="I39" t="s">
-        <v>217</v>
+        <v>195</v>
+      </c>
+      <c r="J39" t="s">
+        <v>191</v>
+      </c>
+      <c r="K39" t="s">
+        <v>192</v>
       </c>
       <c r="L39" t="s">
-        <v>218</v>
+        <v>103</v>
+      </c>
+      <c r="M39" t="s">
+        <v>193</v>
+      </c>
+      <c r="N39" t="s">
+        <v>194</v>
+      </c>
+      <c r="P39" t="s">
+        <v>81</v>
+      </c>
+      <c r="S39" t="s">
+        <v>114</v>
+      </c>
+      <c r="T39" t="s">
+        <v>55</v>
+      </c>
+      <c r="U39" t="s">
+        <v>191</v>
+      </c>
+      <c r="V39" t="s">
+        <v>192</v>
+      </c>
+      <c r="W39" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B40" t="b">
         <v>1</v>
@@ -3018,22 +2969,84 @@
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="E40">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F40" t="s">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="I40" t="s">
-        <v>220</v>
+        <v>218</v>
+      </c>
+      <c r="J40" t="s">
+        <v>207</v>
+      </c>
+      <c r="K40" t="s">
+        <v>208</v>
       </c>
       <c r="L40" t="s">
-        <v>221</v>
-      </c>
-      <c r="Y40" t="s">
-        <v>222</v>
+        <v>206</v>
+      </c>
+      <c r="S40" t="s">
+        <v>171</v>
+      </c>
+      <c r="T40" t="s">
+        <v>55</v>
+      </c>
+      <c r="U40" t="s">
+        <v>207</v>
+      </c>
+      <c r="V40" t="s">
+        <v>208</v>
+      </c>
+      <c r="W40" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>225</v>
+      </c>
+      <c r="B41" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
+        <v>113</v>
+      </c>
+      <c r="H41" t="s">
+        <v>59</v>
+      </c>
+      <c r="I41" t="s">
+        <v>219</v>
+      </c>
+      <c r="J41" t="s">
+        <v>207</v>
+      </c>
+      <c r="K41" t="s">
+        <v>208</v>
+      </c>
+      <c r="L41" t="s">
+        <v>206</v>
+      </c>
+      <c r="S41" t="s">
+        <v>172</v>
+      </c>
+      <c r="T41" t="s">
+        <v>55</v>
+      </c>
+      <c r="U41" t="s">
+        <v>207</v>
+      </c>
+      <c r="V41" t="s">
+        <v>208</v>
+      </c>
+      <c r="W41" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -3043,17 +3056,17 @@
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4">
+  <conditionalFormatting sqref="A5">
     <cfRule type="expression" dxfId="3" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
+  <conditionalFormatting sqref="B5">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
+  <conditionalFormatting sqref="I5">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
